--- a/jobs13C/template.xlsx
+++ b/jobs13C/template.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006F9AC-F8DE-4EDB-AD5A-6BE115C803EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4B3D5C-89C1-4748-8D60-B52542A0D22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6585" yWindow="2565" windowWidth="19305" windowHeight="12270" activeTab="1" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
+    <workbookView xWindow="6585" yWindow="2565" windowWidth="19305" windowHeight="12270" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
   <sheets>
     <sheet name="CHA1C3andC4_20260316" sheetId="1" r:id="rId1"/>
     <sheet name="Swedish_Samples" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -775,13 +774,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25482F99-DBEE-4B34-A671-7B67218A42AE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/jobs13C/template.xlsx
+++ b/jobs13C/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4B3D5C-89C1-4748-8D60-B52542A0D22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC28E65C-163E-4B07-B6DF-AEAFD0E020B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6585" yWindow="2565" windowWidth="19305" windowHeight="12270" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
+    <workbookView xWindow="6585" yWindow="2565" windowWidth="19305" windowHeight="12270" activeTab="1" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
   <sheets>
     <sheet name="CHA1C3andC4_20260316" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
-    <t>file location</t>
-  </si>
-  <si>
     <t>inclusion</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>swedish_samples_metabolomics_pos20260423</t>
+  </si>
+  <si>
+    <t>folder</t>
   </si>
 </sst>
 </file>
@@ -554,145 +554,145 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -728,47 +728,47 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
